--- a/skills/flaggems-pr-submit/data/规范名.xlsx
+++ b/skills/flaggems-pr-submit/data/规范名.xlsx
@@ -9575,7 +9575,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>https://github.com/flagos-ai/FlagGems/pull/4817</t>
         </is>
       </c>
     </row>

--- a/skills/flaggems-pr-submit/data/规范名.xlsx
+++ b/skills/flaggems-pr-submit/data/规范名.xlsx
@@ -1143,7 +1143,8 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/118</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1365,8 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/116</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1553,8 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/114</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1571,8 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/121</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7165,8 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>https://github.com/flagos-ai/FlagGems/pull/3444</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/117</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7438,8 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://github.com/flagos-ai/FlagGems/pull/3470</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/122</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7490,8 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>https://github.com/flagos-ai/FlagGems/pull/3536</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/119</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9888,8 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>https://github.com/flagos-ai/FlagGems/pull/3872</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/120</t>
         </is>
       </c>
     </row>

--- a/skills/flaggems-pr-submit/data/规范名.xlsx
+++ b/skills/flaggems-pr-submit/data/规范名.xlsx
@@ -6740,7 +6740,8 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/129</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8971,8 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/127</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9244,8 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>https://github.com/flagos-ai/FlagGems/pull/3894</t>
+          <t>Warning: 1 uncommitted change
+https://github.com/flagos-ai/FlagGems-Experimental/pull/133</t>
         </is>
       </c>
     </row>
